--- a/Employee_Reports_wi52/Joe Vergil Jr Calanza Dormitorio Q0556.xlsx
+++ b/Employee_Reports_wi52/Joe Vergil Jr Calanza Dormitorio Q0556.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-124</v>
+        <v>-132</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>-127</v>
+        <v>-135</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-322</v>
+        <v>-330</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -922,11 +922,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-311</v>
+        <v>-319</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1069,11 +1069,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1106,11 +1106,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1155,11 +1155,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1204,11 +1204,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1253,11 +1253,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1339,11 +1339,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Reschelying Cart (QNL Trainings)</t>
+          <t>Reshelving Cart (QNL Trainings)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
@@ -1376,11 +1376,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1413,11 +1413,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1450,11 +1450,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1500,6 +1500,43 @@
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>LIFTER (QNL Trainings)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>05-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>04-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>707</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
